--- a/app/data/catalogues/SemSac_juridictions.xlsx
+++ b/app/data/catalogues/SemSac_juridictions.xlsx
@@ -3513,7 +3513,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Castelnau-Montratier (Lot, France)</t>
+          <t>Castelnau Montratier-Sainte Alauzie (Lot, France)</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Castelnau-Montratier (Lot, France)</t>
+          <t>Castelnau Montratier-Sainte Alauzie (Lot, France)</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Castelnau-Montratier (Lot, France)</t>
+          <t>Castelnau Montratier-Sainte Alauzie (Lot, France)</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Lasserrade (Gers, France)</t>
+          <t>Lasserade (Gers, France)</t>
         </is>
       </c>
     </row>
@@ -13681,7 +13681,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Montgailhard (Ariège, France)</t>
+          <t>Montgaillard (Ariège, France)</t>
         </is>
       </c>
     </row>
@@ -16232,7 +16232,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Mont-de-Randon (Lozère, France)</t>
+          <t>Monts-de-Randon (Lozère, France)</t>
         </is>
       </c>
     </row>
